--- a/excel/18图表与Offset函数.xlsx
+++ b/excel/18图表与Offset函数.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10830"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D19A3B6-AFEE-0E48-A03A-AE6F141BEC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4EDF4C8-299C-4F45-9D00-7F2A03580EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXCEL课件" sheetId="1" r:id="rId1"/>
@@ -21,21 +21,15 @@
     <sheet name="虚拟法" sheetId="9" r:id="rId6"/>
     <sheet name="误差法" sheetId="10" r:id="rId7"/>
     <sheet name="其它图表" sheetId="11" r:id="rId8"/>
-    <sheet name="我的练习" sheetId="4" r:id="rId9"/>
-    <sheet name="Offset动态图表" sheetId="2" r:id="rId10"/>
+    <sheet name="Offset动态图表" sheetId="2" r:id="rId9"/>
+    <sheet name="我的练习" sheetId="4" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">其它图表!$B$83:$C$110</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">其它图表!$D$82</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">其它图表!$D$83:$D$110</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">其它图表!$A$1:$C$110</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">其它图表!$D$82</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">其它图表!$D$83:$D$110</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">其它图表!$B$83:$C$110</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">其它图表!$D$82</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">其它图表!$D$83:$D$110</definedName>
-    <definedName name="最后五天开盘价" localSheetId="9">OFFSET(Offset动态图表!$B$1,COUNTA(Offset动态图表!$B:$B)-5,0,5,1)</definedName>
-    <definedName name="最后五天日期" localSheetId="9">OFFSET(Offset动态图表!$A$1,COUNTA(Offset动态图表!$A:$A)-5,0,5,1)</definedName>
+    <definedName name="最后五天开盘价" localSheetId="8">OFFSET(Offset动态图表!$B$1,COUNTA(Offset动态图表!$B:$B)-5,0,5,1)</definedName>
+    <definedName name="最后五天日期" localSheetId="8">OFFSET(Offset动态图表!$A$1,COUNTA(Offset动态图表!$A:$A)-5,0,5,1)</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
@@ -1567,12 +1561,12 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
-    <numFmt numFmtId="179" formatCode="\a"/>
-    <numFmt numFmtId="180" formatCode="&quot;b&quot;"/>
-    <numFmt numFmtId="181" formatCode="\c"/>
-    <numFmt numFmtId="182" formatCode="&quot;D&quot;"/>
-    <numFmt numFmtId="183" formatCode="\f"/>
-    <numFmt numFmtId="184" formatCode="0.0_);[Red]\(0.0\)"/>
+    <numFmt numFmtId="178" formatCode="\a"/>
+    <numFmt numFmtId="179" formatCode="&quot;b&quot;"/>
+    <numFmt numFmtId="180" formatCode="\c"/>
+    <numFmt numFmtId="181" formatCode="&quot;D&quot;"/>
+    <numFmt numFmtId="182" formatCode="\f"/>
+    <numFmt numFmtId="183" formatCode="0.0_);[Red]\(0.0\)"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -2029,7 +2023,7 @@
     <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -2077,7 +2071,7 @@
     <xf numFmtId="0" fontId="24" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2086,19 +2080,19 @@
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5773,34 +5767,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>24</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>64</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>98</c:v>
+                  <c:v>82</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>44</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>100</c:v>
+                  <c:v>99</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>95</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>52</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>81</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>36</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7189,7 +7183,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{5BE56CC3-8ADB-AB44-8D26-E5B24468D3F0}" type="CELLRANGE">
-                      <a:rPr lang="en-US" altLang="zh-CN"/>
+                      <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -7222,7 +7216,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{FC10A540-F802-8748-A546-E486F5F34989}" type="CELLRANGE">
-                      <a:rPr lang="en-US" altLang="zh-CN"/>
+                      <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -7255,7 +7249,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{4E6FC41F-B8DA-4D42-9112-37CA42622F92}" type="CELLRANGE">
-                      <a:rPr lang="en-US" altLang="zh-CN"/>
+                      <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -7288,7 +7282,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{81B3A574-7679-5E48-9B60-D50CAA90291E}" type="CELLRANGE">
-                      <a:rPr lang="en-US" altLang="zh-CN"/>
+                      <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -7321,7 +7315,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{F1C826AD-DE97-8043-857A-DF4F88530201}" type="CELLRANGE">
-                      <a:rPr lang="en-US" altLang="zh-CN"/>
+                      <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -7354,7 +7348,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{47AD2C1E-AAF6-1F45-BF97-664999DBBA53}" type="CELLRANGE">
-                      <a:rPr lang="en-US" altLang="zh-CN"/>
+                      <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -7387,7 +7381,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{21FF35FA-8F3B-D54A-ADB5-4E9E59886DA0}" type="CELLRANGE">
-                      <a:rPr lang="en-US" altLang="zh-CN"/>
+                      <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -7420,7 +7414,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{D1FD6BD3-F2D5-7D41-B6B6-B40635823BD8}" type="CELLRANGE">
-                      <a:rPr lang="en-US" altLang="zh-CN"/>
+                      <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -7453,7 +7447,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{31E920CB-341F-2E42-A202-EC35CCC2C133}" type="CELLRANGE">
-                      <a:rPr lang="en-US" altLang="zh-CN"/>
+                      <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -7486,7 +7480,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{254AF7EE-0303-104B-8CEC-84077717A7BE}" type="CELLRANGE">
-                      <a:rPr lang="en-US" altLang="zh-CN"/>
+                      <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -10631,7 +10625,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{372411CE-AE2B-8A44-8E90-2F700115C263}" type="CELLRANGE">
+                    <a:fld id="{FFB863A6-E62F-044C-83EA-947938F50E53}" type="CELLRANGE">
                       <a:rPr lang="en-US" altLang="zh-CN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10664,7 +10658,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EBD30E79-23B3-764B-ABC4-A97A9CF3FEBA}" type="CELLRANGE">
+                    <a:fld id="{F8064FE1-E792-F646-8DE2-FCB421310801}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10698,7 +10692,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1D950504-88F5-F64A-8A85-AFF0194DA3EE}" type="CELLRANGE">
+                    <a:fld id="{37644C7D-09A4-3348-B26B-6A4F2390394F}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10732,7 +10726,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6754496A-1D72-3640-B035-B7EEBD4EEBFF}" type="CELLRANGE">
+                    <a:fld id="{EC64FB5E-15E3-BF4E-916C-21237A64C1EC}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10766,7 +10760,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D856F9DE-7CE3-7C4F-B649-9227F8FB60D0}" type="CELLRANGE">
+                    <a:fld id="{80754EDC-C66A-D54C-A7D0-B2D255861DAC}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10800,7 +10794,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2CA9F146-EC69-8C4A-9940-D8A86B2B6424}" type="CELLRANGE">
+                    <a:fld id="{F16A21AF-78EA-994B-912E-E46D7C88DBBB}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10834,7 +10828,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7EAFB84D-60E9-0740-85E8-C5B520C1B81D}" type="CELLRANGE">
+                    <a:fld id="{E12BFA4F-2CB2-074E-9E29-751E0AA92CD1}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10868,7 +10862,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{42CA3E61-EF64-0345-9496-4106A7C8B082}" type="CELLRANGE">
+                    <a:fld id="{87C0AD53-F15D-9A42-8A92-05B326ADCDCF}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10902,7 +10896,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{688E0199-D1B2-494E-91C1-1A43F0D604B0}" type="CELLRANGE">
+                    <a:fld id="{2597B977-A6F8-914A-B902-B3E62BFE50C0}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10936,7 +10930,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FC7A4F90-167C-DD40-8D18-DFB9BFCD8B67}" type="CELLRANGE">
+                    <a:fld id="{1734C51C-87E3-784A-8633-73A31BFD7DB1}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10970,7 +10964,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{02637668-D071-7444-93D3-941381866F9D}" type="CELLRANGE">
+                    <a:fld id="{326C693D-AC8C-1E4D-A5B4-1E4D40506A91}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -11004,7 +10998,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B0F298E9-8CBC-514B-98E5-FC6F089586F5}" type="CELLRANGE">
+                    <a:fld id="{E57CB049-3F7D-D548-B87F-75280EAC4065}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -12291,6 +12285,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-B115-E242-B46B-C83F4244397E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -13230,8 +13229,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A563EFA2-39FC-EB4E-97A8-45D568798693}" type="CELLRANGE">
-                      <a:rPr lang="zh-CN" altLang="en-US"/>
+                    <a:fld id="{309C7BF0-EB9D-6346-A799-FC47CF4A2EF2}" type="CELLRANGE">
+                      <a:rPr lang="en-US" altLang="zh-CN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -13263,7 +13262,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BC82912E-8753-5B4F-B5D1-BF961CA2227E}" type="CELLRANGE">
+                    <a:fld id="{54606D6D-1DD8-D04F-953C-B5FCEF00CEE2}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13297,7 +13296,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6594FABB-3957-8043-8761-3EC5FE3C134C}" type="CELLRANGE">
+                    <a:fld id="{623416E7-C604-D647-88A3-C99DC995E6C3}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13331,7 +13330,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{26E27D44-D58F-464D-9A73-C53D4A91AD50}" type="CELLRANGE">
+                    <a:fld id="{1057A687-E7E2-5541-A30F-B518BD26E138}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13365,7 +13364,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8BD7F817-E898-4548-83A6-35515DC24DD6}" type="CELLRANGE">
+                    <a:fld id="{8728E0E6-031D-6A46-9604-A11A3D4EFD1F}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13399,7 +13398,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E93BE3D9-D5B1-8746-B434-8B83F0A1EB32}" type="CELLRANGE">
+                    <a:fld id="{98659C89-3E1B-F94A-A21A-96D953669F27}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13433,7 +13432,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B2F78218-6894-8647-8ED3-870735252472}" type="CELLRANGE">
+                    <a:fld id="{9EC53A83-43BF-3348-8046-B085B68B6683}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13467,7 +13466,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{42045E28-B1FA-7547-BD0C-3E0A0D60F568}" type="CELLRANGE">
+                    <a:fld id="{AF223B53-FB61-1F45-88D7-B56D3CA7CF29}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14191,6 +14190,355 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-CN"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Offset动态图表!最后五天日期</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy/m/d;@</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>44357</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44358</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44362</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>44363</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>44364</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Offset动态图表!最后五天开盘价</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2238.48</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2178.81</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2193</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2158</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2156.91</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E956-5D44-9DAB-D03EFD20E188}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1016265600"/>
+        <c:axId val="223781183"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1016265600"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy/m/d;@" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="223781183"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="223781183"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1016265600"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart28.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
@@ -14820,355 +15168,6 @@
         </a:p>
       </c:txPr>
     </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="zh-CN"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart28.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="zh-CN"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="zh-CN"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="t"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:numRef>
-              <c:f>Offset动态图表!最后五天日期</c:f>
-              <c:numCache>
-                <c:formatCode>yyyy/m/d;@</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>44357</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>44358</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>44362</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>44363</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>44364</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Offset动态图表!最后五天开盘价</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>2238.48</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2178.81</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2193</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2158</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2156.91</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E956-5D44-9DAB-D03EFD20E188}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="t"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="1016265600"/>
-        <c:axId val="223781183"/>
-      </c:lineChart>
-      <c:dateAx>
-        <c:axId val="1016265600"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="yyyy/m/d;@" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="zh-CN"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="223781183"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblOffset val="100"/>
-        <c:baseTimeUnit val="days"/>
-      </c:dateAx>
-      <c:valAx>
-        <c:axId val="223781183"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="zh-CN"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1016265600"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -19558,10 +19557,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.6</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="size">
-        <cx:f>_xlchart.v1.8</cx:f>
+        <cx:f>_xlchart.v1.2</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -19571,7 +19570,7 @@
         <cx:series layoutId="treemap" uniqueId="{00000000-8AB7-A94C-8831-50B1B396E1F1}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.7</cx:f>
+              <cx:f>_xlchart.v1.1</cx:f>
               <cx:v>求和项:金额</cx:v>
             </cx:txData>
           </cx:tx>
@@ -29961,7 +29960,7 @@
 </file>
 
 <file path=xl/charts/style26.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -30069,6 +30068,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -30079,6 +30083,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -30110,6 +30119,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -30464,7 +30476,7 @@
 </file>
 
 <file path=xl/charts/style27.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -30572,11 +30584,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -30587,11 +30594,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -30623,9 +30625,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -34817,23 +34816,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>355600</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>21165</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>16934</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>778934</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>33867</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>783166</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>27516</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="图表 2">
+        <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -36410,7 +36409,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5863165" y="15289741"/>
+              <a:off x="5869515" y="15289741"/>
               <a:ext cx="4995335" cy="5524500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -36837,23 +36836,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>21165</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>16934</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>783166</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>27516</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>778934</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>33867</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="图表 1">
+        <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -37623,198 +37622,145 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B5A2384-4132-C24C-9A85-82E90AE19F3C}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F29A085-C218-024F-872C-830C0CCFCAF5}">
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="11">
-        <v>44365</v>
-      </c>
-      <c r="E1" s="12">
-        <v>2090.94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="11">
-        <v>44351</v>
-      </c>
-      <c r="B2" s="12">
-        <v>2251.5</v>
-      </c>
-      <c r="D2" s="11">
-        <v>44368</v>
-      </c>
-      <c r="E2" s="12">
-        <v>2081.64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="11">
-        <v>44354</v>
-      </c>
-      <c r="B3" s="12">
-        <v>2271</v>
-      </c>
-      <c r="D3" s="11">
-        <v>44369</v>
-      </c>
-      <c r="E3" s="12">
-        <v>2074.9699999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="11">
-        <v>44355</v>
-      </c>
-      <c r="B4" s="12">
-        <v>2191</v>
-      </c>
-      <c r="D4" s="11">
-        <v>44370</v>
-      </c>
-      <c r="E4" s="12">
-        <v>2038</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="11">
-        <v>44356</v>
-      </c>
-      <c r="B5" s="12">
-        <v>2199.5</v>
-      </c>
-      <c r="D5" s="11">
-        <v>44371</v>
-      </c>
-      <c r="E5" s="12">
-        <v>2068.0500000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="11">
-        <v>44357</v>
-      </c>
-      <c r="B6" s="12">
-        <v>2238.48</v>
-      </c>
-      <c r="D6" s="11">
-        <v>44372</v>
-      </c>
-      <c r="E6" s="12">
-        <v>2092</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="11">
-        <v>44358</v>
-      </c>
-      <c r="B7" s="12">
-        <v>2178.81</v>
-      </c>
-      <c r="D7" s="11">
-        <v>44375</v>
-      </c>
-      <c r="E7" s="12">
-        <v>2103.0100000000002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="11">
-        <v>44362</v>
-      </c>
-      <c r="B8" s="12">
-        <v>2193</v>
-      </c>
-      <c r="D8" s="11">
-        <v>44376</v>
-      </c>
-      <c r="E8" s="12">
-        <v>2062</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="11">
-        <v>44363</v>
-      </c>
-      <c r="B9" s="12">
-        <v>2158</v>
-      </c>
-      <c r="D9" s="11">
-        <v>44377</v>
-      </c>
-      <c r="E9" s="12">
-        <v>2056.6999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="11">
-        <v>44364</v>
-      </c>
-      <c r="B10" s="12">
-        <v>2156.91</v>
-      </c>
-      <c r="D10" s="11">
-        <v>44378</v>
-      </c>
-      <c r="E10" s="12">
-        <v>2105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="C13" s="13" cm="1">
-        <f t="array" aca="1" ref="C13:C17" ca="1">最后五天日期</f>
-        <v>44357</v>
-      </c>
-      <c r="D13" cm="1">
-        <f t="array" aca="1" ref="D13:D17" ca="1">最后五天开盘价</f>
-        <v>2238.48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="C14">
-        <f ca="1"/>
-        <v>44358</v>
-      </c>
-      <c r="D14">
-        <f ca="1"/>
-        <v>2178.81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="C15">
-        <f ca="1"/>
-        <v>44362</v>
-      </c>
-      <c r="D15">
-        <f ca="1"/>
-        <v>2193</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="C16">
-        <f ca="1"/>
-        <v>44363</v>
-      </c>
-      <c r="D16">
-        <f ca="1"/>
-        <v>2158</v>
-      </c>
-    </row>
-    <row r="17" spans="3:4">
-      <c r="C17">
-        <f ca="1"/>
-        <v>44364</v>
-      </c>
-      <c r="D17">
-        <f ca="1"/>
-        <v>2156.91</v>
+    <row r="1" spans="1:4">
+      <c r="A1" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="17">
+        <v>45000</v>
+      </c>
+      <c r="C2" s="17">
+        <v>44521</v>
+      </c>
+      <c r="D2" s="27">
+        <f>C2/B2</f>
+        <v>0.98935555555555554</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" s="17">
+        <v>25000</v>
+      </c>
+      <c r="C3" s="17">
+        <v>24821</v>
+      </c>
+      <c r="D3" s="27">
+        <f t="shared" ref="D3:D9" si="0">C3/B3</f>
+        <v>0.99283999999999994</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="17">
+        <v>11000</v>
+      </c>
+      <c r="C4" s="17">
+        <v>10798</v>
+      </c>
+      <c r="D4" s="27">
+        <f t="shared" si="0"/>
+        <v>0.98163636363636364</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="17">
+        <v>7000</v>
+      </c>
+      <c r="C5" s="17">
+        <v>6799</v>
+      </c>
+      <c r="D5" s="27">
+        <f t="shared" si="0"/>
+        <v>0.97128571428571431</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="17">
+        <v>6650</v>
+      </c>
+      <c r="C6" s="17">
+        <v>6550</v>
+      </c>
+      <c r="D6" s="27">
+        <f t="shared" si="0"/>
+        <v>0.98496240601503759</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="17">
+        <v>1200</v>
+      </c>
+      <c r="C7" s="17">
+        <v>1189</v>
+      </c>
+      <c r="D7" s="27">
+        <f t="shared" si="0"/>
+        <v>0.99083333333333334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="17">
+        <v>1100</v>
+      </c>
+      <c r="C8" s="17">
+        <v>1098</v>
+      </c>
+      <c r="D8" s="27">
+        <f t="shared" si="0"/>
+        <v>0.99818181818181817</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="17">
+        <v>900</v>
+      </c>
+      <c r="C9" s="17">
+        <v>893</v>
+      </c>
+      <c r="D9" s="27">
+        <f t="shared" si="0"/>
+        <v>0.99222222222222223</v>
       </c>
     </row>
   </sheetData>
@@ -41009,7 +40955,7 @@
       </c>
       <c r="B2" s="21">
         <f ca="1">RANDBETWEEN(0,100)</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -41024,7 +40970,7 @@
       </c>
       <c r="B3" s="21">
         <f t="shared" ref="B3:B11" ca="1" si="0">RANDBETWEEN(0,100)</f>
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -41039,7 +40985,7 @@
       </c>
       <c r="B4" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -41048,7 +40994,7 @@
       </c>
       <c r="B5" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -41057,7 +41003,7 @@
       </c>
       <c r="B6" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -41066,7 +41012,7 @@
       </c>
       <c r="B7" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -41075,7 +41021,7 @@
       </c>
       <c r="B8" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -41084,7 +41030,7 @@
       </c>
       <c r="B9" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -41093,7 +41039,7 @@
       </c>
       <c r="B10" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -41102,7 +41048,7 @@
       </c>
       <c r="B11" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -43263,145 +43209,198 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F29A085-C218-024F-872C-830C0CCFCAF5}">
-  <dimension ref="A1:D9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B5A2384-4132-C24C-9A85-82E90AE19F3C}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" s="17">
-        <v>45000</v>
-      </c>
-      <c r="C2" s="17">
-        <v>44521</v>
-      </c>
-      <c r="D2" s="27">
-        <f>C2/B2</f>
-        <v>0.98935555555555554</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="17">
-        <v>25000</v>
-      </c>
-      <c r="C3" s="17">
-        <v>24821</v>
-      </c>
-      <c r="D3" s="27">
-        <f t="shared" ref="D3:D9" si="0">C3/B3</f>
-        <v>0.99283999999999994</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="B4" s="17">
-        <v>11000</v>
-      </c>
-      <c r="C4" s="17">
-        <v>10798</v>
-      </c>
-      <c r="D4" s="27">
-        <f t="shared" si="0"/>
-        <v>0.98163636363636364</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="17">
-        <v>7000</v>
-      </c>
-      <c r="C5" s="17">
-        <v>6799</v>
-      </c>
-      <c r="D5" s="27">
-        <f t="shared" si="0"/>
-        <v>0.97128571428571431</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="B6" s="17">
-        <v>6650</v>
-      </c>
-      <c r="C6" s="17">
-        <v>6550</v>
-      </c>
-      <c r="D6" s="27">
-        <f t="shared" si="0"/>
-        <v>0.98496240601503759</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="B7" s="17">
-        <v>1200</v>
-      </c>
-      <c r="C7" s="17">
-        <v>1189</v>
-      </c>
-      <c r="D7" s="27">
-        <f t="shared" si="0"/>
-        <v>0.99083333333333334</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="B8" s="17">
-        <v>1100</v>
-      </c>
-      <c r="C8" s="17">
-        <v>1098</v>
-      </c>
-      <c r="D8" s="27">
-        <f t="shared" si="0"/>
-        <v>0.99818181818181817</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="B9" s="17">
-        <v>900</v>
-      </c>
-      <c r="C9" s="17">
-        <v>893</v>
-      </c>
-      <c r="D9" s="27">
-        <f t="shared" si="0"/>
-        <v>0.99222222222222223</v>
+    <row r="1" spans="1:5">
+      <c r="A1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="11">
+        <v>44365</v>
+      </c>
+      <c r="E1" s="12">
+        <v>2090.94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="11">
+        <v>44351</v>
+      </c>
+      <c r="B2" s="12">
+        <v>2251.5</v>
+      </c>
+      <c r="D2" s="11">
+        <v>44368</v>
+      </c>
+      <c r="E2" s="12">
+        <v>2081.64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="11">
+        <v>44354</v>
+      </c>
+      <c r="B3" s="12">
+        <v>2271</v>
+      </c>
+      <c r="D3" s="11">
+        <v>44369</v>
+      </c>
+      <c r="E3" s="12">
+        <v>2074.9699999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="11">
+        <v>44355</v>
+      </c>
+      <c r="B4" s="12">
+        <v>2191</v>
+      </c>
+      <c r="D4" s="11">
+        <v>44370</v>
+      </c>
+      <c r="E4" s="12">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="11">
+        <v>44356</v>
+      </c>
+      <c r="B5" s="12">
+        <v>2199.5</v>
+      </c>
+      <c r="D5" s="11">
+        <v>44371</v>
+      </c>
+      <c r="E5" s="12">
+        <v>2068.0500000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="11">
+        <v>44357</v>
+      </c>
+      <c r="B6" s="12">
+        <v>2238.48</v>
+      </c>
+      <c r="D6" s="11">
+        <v>44372</v>
+      </c>
+      <c r="E6" s="12">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="11">
+        <v>44358</v>
+      </c>
+      <c r="B7" s="12">
+        <v>2178.81</v>
+      </c>
+      <c r="D7" s="11">
+        <v>44375</v>
+      </c>
+      <c r="E7" s="12">
+        <v>2103.0100000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="11">
+        <v>44362</v>
+      </c>
+      <c r="B8" s="12">
+        <v>2193</v>
+      </c>
+      <c r="D8" s="11">
+        <v>44376</v>
+      </c>
+      <c r="E8" s="12">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="11">
+        <v>44363</v>
+      </c>
+      <c r="B9" s="12">
+        <v>2158</v>
+      </c>
+      <c r="D9" s="11">
+        <v>44377</v>
+      </c>
+      <c r="E9" s="12">
+        <v>2056.6999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="11">
+        <v>44364</v>
+      </c>
+      <c r="B10" s="12">
+        <v>2156.91</v>
+      </c>
+      <c r="D10" s="11">
+        <v>44378</v>
+      </c>
+      <c r="E10" s="12">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="C13" s="13" cm="1">
+        <f t="array" aca="1" ref="C13:C17" ca="1">最后五天日期</f>
+        <v>44357</v>
+      </c>
+      <c r="D13" cm="1">
+        <f t="array" aca="1" ref="D13:D17" ca="1">最后五天开盘价</f>
+        <v>2238.48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="C14">
+        <f ca="1"/>
+        <v>44358</v>
+      </c>
+      <c r="D14">
+        <f ca="1"/>
+        <v>2178.81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="C15">
+        <f ca="1"/>
+        <v>44362</v>
+      </c>
+      <c r="D15">
+        <f ca="1"/>
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="C16">
+        <f ca="1"/>
+        <v>44363</v>
+      </c>
+      <c r="D16">
+        <f ca="1"/>
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4">
+      <c r="C17">
+        <f ca="1"/>
+        <v>44364</v>
+      </c>
+      <c r="D17">
+        <f ca="1"/>
+        <v>2156.91</v>
       </c>
     </row>
   </sheetData>

--- a/excel/18图表与Offset函数.xlsx
+++ b/excel/18图表与Offset函数.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4EDF4C8-299C-4F45-9D00-7F2A03580EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EA32ED-AB6D-1044-9202-C48F98137D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXCEL课件" sheetId="1" r:id="rId1"/>
@@ -5767,34 +5767,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>36</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>82</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>99</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>92</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>62</c:v>
-                </c:pt>
                 <c:pt idx="8">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>96</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7182,8 +7182,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5BE56CC3-8ADB-AB44-8D26-E5B24468D3F0}" type="CELLRANGE">
-                      <a:rPr lang="zh-CN" altLang="en-US"/>
+                    <a:fld id="{BB96EB1A-A703-334A-B5F3-C5EF1164DBBE}" type="CELLRANGE">
+                      <a:rPr lang="en-US" altLang="zh-CN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -7215,7 +7215,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FC10A540-F802-8748-A546-E486F5F34989}" type="CELLRANGE">
+                    <a:fld id="{4143236F-18B0-E84E-B67B-4236FE8269C8}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7234,6 +7234,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -7248,7 +7249,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4E6FC41F-B8DA-4D42-9112-37CA42622F92}" type="CELLRANGE">
+                    <a:fld id="{1ADB54CF-D48A-BC4B-A434-2C72541FAC29}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7267,6 +7268,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -7281,7 +7283,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{81B3A574-7679-5E48-9B60-D50CAA90291E}" type="CELLRANGE">
+                    <a:fld id="{FC75BE28-7FEE-F745-92C2-050CB34F3C98}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7300,6 +7302,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -7314,7 +7317,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F1C826AD-DE97-8043-857A-DF4F88530201}" type="CELLRANGE">
+                    <a:fld id="{A573F44B-47E1-664D-B183-CB750B9C9B42}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7333,6 +7336,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -7347,7 +7351,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{47AD2C1E-AAF6-1F45-BF97-664999DBBA53}" type="CELLRANGE">
+                    <a:fld id="{95740648-2E72-344E-B800-7E3DC5068D89}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7366,6 +7370,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -7380,7 +7385,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{21FF35FA-8F3B-D54A-ADB5-4E9E59886DA0}" type="CELLRANGE">
+                    <a:fld id="{61ADDC5A-C6A3-AD42-A850-02D54B726E3A}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7399,6 +7404,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -7413,7 +7419,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D1FD6BD3-F2D5-7D41-B6B6-B40635823BD8}" type="CELLRANGE">
+                    <a:fld id="{9157FDA4-7C3D-484A-8501-6781383D627D}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7432,6 +7438,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -7446,7 +7453,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{31E920CB-341F-2E42-A202-EC35CCC2C133}" type="CELLRANGE">
+                    <a:fld id="{5B2838F2-65D6-674E-8F2C-F77F46C9ADA2}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7465,6 +7472,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -7479,7 +7487,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{254AF7EE-0303-104B-8CEC-84077717A7BE}" type="CELLRANGE">
+                    <a:fld id="{ED814AC1-E316-7642-A84C-2BD324C64ECC}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7498,6 +7506,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -10625,7 +10634,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FFB863A6-E62F-044C-83EA-947938F50E53}" type="CELLRANGE">
+                    <a:fld id="{7C840D4D-5D6B-AB4E-811A-266A88A9CA6B}" type="CELLRANGE">
                       <a:rPr lang="en-US" altLang="zh-CN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10658,7 +10667,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F8064FE1-E792-F646-8DE2-FCB421310801}" type="CELLRANGE">
+                    <a:fld id="{15239D6E-DE6D-BC4B-9C4F-CAF6940F6F9B}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10692,7 +10701,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{37644C7D-09A4-3348-B26B-6A4F2390394F}" type="CELLRANGE">
+                    <a:fld id="{C89D5424-748B-4247-810B-0E1FDE640911}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10726,7 +10735,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EC64FB5E-15E3-BF4E-916C-21237A64C1EC}" type="CELLRANGE">
+                    <a:fld id="{74D8067C-0D2A-7B45-84BA-9CDAFB8CE726}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10760,7 +10769,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{80754EDC-C66A-D54C-A7D0-B2D255861DAC}" type="CELLRANGE">
+                    <a:fld id="{9E1FF873-4246-CE4A-980A-20F8446876E7}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10794,7 +10803,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F16A21AF-78EA-994B-912E-E46D7C88DBBB}" type="CELLRANGE">
+                    <a:fld id="{34101729-5F46-D64E-AB26-38799FB0E002}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10828,7 +10837,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E12BFA4F-2CB2-074E-9E29-751E0AA92CD1}" type="CELLRANGE">
+                    <a:fld id="{FF45897F-9E6D-6C41-9F92-6AA5A06274DF}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10862,7 +10871,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{87C0AD53-F15D-9A42-8A92-05B326ADCDCF}" type="CELLRANGE">
+                    <a:fld id="{37F63A4C-30C6-824F-BCEA-69F92CE78EC5}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10896,7 +10905,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2597B977-A6F8-914A-B902-B3E62BFE50C0}" type="CELLRANGE">
+                    <a:fld id="{084FE804-60EF-3C45-A6FD-0EC980EA6D9A}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10930,7 +10939,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1734C51C-87E3-784A-8633-73A31BFD7DB1}" type="CELLRANGE">
+                    <a:fld id="{08C6C62E-842D-9F40-9D13-1D53344E9064}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10964,7 +10973,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{326C693D-AC8C-1E4D-A5B4-1E4D40506A91}" type="CELLRANGE">
+                    <a:fld id="{3B8A2C23-801A-A14C-B336-DE53D9D1F777}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10998,7 +11007,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E57CB049-3F7D-D548-B87F-75280EAC4065}" type="CELLRANGE">
+                    <a:fld id="{FE549127-C35C-624A-AB10-8A0FD38227C8}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13230,7 +13239,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{309C7BF0-EB9D-6346-A799-FC47CF4A2EF2}" type="CELLRANGE">
-                      <a:rPr lang="en-US" altLang="zh-CN"/>
+                      <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -13262,7 +13271,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{54606D6D-1DD8-D04F-953C-B5FCEF00CEE2}" type="CELLRANGE">
+                    <a:fld id="{7F5126BA-824D-634F-BCFF-41DFBCA6E049}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13296,7 +13305,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{623416E7-C604-D647-88A3-C99DC995E6C3}" type="CELLRANGE">
+                    <a:fld id="{90EDFEC5-F7D7-8940-A6F7-38320D828DF8}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13330,7 +13339,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1057A687-E7E2-5541-A30F-B518BD26E138}" type="CELLRANGE">
+                    <a:fld id="{BACF01A6-C078-E845-B470-5C463ED432AD}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13364,7 +13373,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8728E0E6-031D-6A46-9604-A11A3D4EFD1F}" type="CELLRANGE">
+                    <a:fld id="{E5BA5666-B6D5-2F4D-9F2A-DA25D7679A79}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13398,7 +13407,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{98659C89-3E1B-F94A-A21A-96D953669F27}" type="CELLRANGE">
+                    <a:fld id="{BD3ECF35-9561-3C40-A2A1-1723818B1F05}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13432,7 +13441,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9EC53A83-43BF-3348-8046-B085B68B6683}" type="CELLRANGE">
+                    <a:fld id="{3BEA2FEF-BD48-DB40-BB97-A1E4B880B3C2}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13466,7 +13475,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AF223B53-FB61-1F45-88D7-B56D3CA7CF29}" type="CELLRANGE">
+                    <a:fld id="{655316A2-33C2-2E41-8413-4A8789525476}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -40955,7 +40964,7 @@
       </c>
       <c r="B2" s="21">
         <f ca="1">RANDBETWEEN(0,100)</f>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -40970,7 +40979,7 @@
       </c>
       <c r="B3" s="21">
         <f t="shared" ref="B3:B11" ca="1" si="0">RANDBETWEEN(0,100)</f>
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -40985,7 +40994,7 @@
       </c>
       <c r="B4" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -40994,7 +41003,7 @@
       </c>
       <c r="B5" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -41003,7 +41012,7 @@
       </c>
       <c r="B6" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -41012,7 +41021,7 @@
       </c>
       <c r="B7" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>92</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -41021,7 +41030,7 @@
       </c>
       <c r="B8" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -41030,7 +41039,7 @@
       </c>
       <c r="B9" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -41039,7 +41048,7 @@
       </c>
       <c r="B10" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -41048,7 +41057,7 @@
       </c>
       <c r="B11" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:5">

--- a/excel/18图表与Offset函数.xlsx
+++ b/excel/18图表与Offset函数.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EA32ED-AB6D-1044-9202-C48F98137D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA8BD82-735B-A64D-98D6-74A2CF413394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5767,34 +5767,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>71</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>49</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>91</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>27</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>99</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>85</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>96</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7183,7 +7183,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:fld id="{BB96EB1A-A703-334A-B5F3-C5EF1164DBBE}" type="CELLRANGE">
-                      <a:rPr lang="en-US" altLang="zh-CN"/>
+                      <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -7215,7 +7215,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4143236F-18B0-E84E-B67B-4236FE8269C8}" type="CELLRANGE">
+                    <a:fld id="{8FC02C76-8C65-DD45-B349-7FF5BADB4F7A}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7249,7 +7249,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1ADB54CF-D48A-BC4B-A434-2C72541FAC29}" type="CELLRANGE">
+                    <a:fld id="{0EBB2D3B-394A-174E-81EC-378252E71DBC}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7283,7 +7283,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FC75BE28-7FEE-F745-92C2-050CB34F3C98}" type="CELLRANGE">
+                    <a:fld id="{EE9FD751-50B8-EA44-91A4-FAA5044FE4F9}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7317,7 +7317,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A573F44B-47E1-664D-B183-CB750B9C9B42}" type="CELLRANGE">
+                    <a:fld id="{8985506C-217B-8E47-B9C2-001E9AC4E228}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7351,7 +7351,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{95740648-2E72-344E-B800-7E3DC5068D89}" type="CELLRANGE">
+                    <a:fld id="{4991E127-E0A5-1B40-95C1-412CDA3364BB}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7385,7 +7385,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{61ADDC5A-C6A3-AD42-A850-02D54B726E3A}" type="CELLRANGE">
+                    <a:fld id="{9AF4FB9B-2993-8F4D-9B27-968617EA38B6}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7419,7 +7419,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9157FDA4-7C3D-484A-8501-6781383D627D}" type="CELLRANGE">
+                    <a:fld id="{527A3373-473A-6241-A6F9-57187D6284D2}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7453,7 +7453,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5B2838F2-65D6-674E-8F2C-F77F46C9ADA2}" type="CELLRANGE">
+                    <a:fld id="{3DABFF05-1D9E-7245-8582-3384B415A81C}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7487,7 +7487,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ED814AC1-E316-7642-A84C-2BD324C64ECC}" type="CELLRANGE">
+                    <a:fld id="{6D44C7E4-5146-2B42-B5D2-976307A957A8}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10634,7 +10634,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7C840D4D-5D6B-AB4E-811A-266A88A9CA6B}" type="CELLRANGE">
+                    <a:fld id="{BC535534-C589-294E-B5A5-856B6BB0B195}" type="CELLRANGE">
                       <a:rPr lang="en-US" altLang="zh-CN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10667,7 +10667,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{15239D6E-DE6D-BC4B-9C4F-CAF6940F6F9B}" type="CELLRANGE">
+                    <a:fld id="{B0EC9C77-57F3-6042-9885-BC5B7C98A499}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10701,7 +10701,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C89D5424-748B-4247-810B-0E1FDE640911}" type="CELLRANGE">
+                    <a:fld id="{F02DFB9E-4299-5C4C-AC10-90D321ED0995}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10735,7 +10735,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{74D8067C-0D2A-7B45-84BA-9CDAFB8CE726}" type="CELLRANGE">
+                    <a:fld id="{CD5D7E2B-348F-7742-8FFC-517DFB61885B}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10769,7 +10769,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9E1FF873-4246-CE4A-980A-20F8446876E7}" type="CELLRANGE">
+                    <a:fld id="{113D75BD-9392-E747-8E7E-6BFF6226CEB4}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10803,7 +10803,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{34101729-5F46-D64E-AB26-38799FB0E002}" type="CELLRANGE">
+                    <a:fld id="{3D1982F4-07C9-854F-9AB0-7343987269C4}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10837,7 +10837,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FF45897F-9E6D-6C41-9F92-6AA5A06274DF}" type="CELLRANGE">
+                    <a:fld id="{543C366E-A16B-9E4B-9800-30E42A86E4C0}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10871,7 +10871,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{37F63A4C-30C6-824F-BCEA-69F92CE78EC5}" type="CELLRANGE">
+                    <a:fld id="{38A9E32D-FA9A-EF49-A80F-C77FDC572B54}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10905,7 +10905,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{084FE804-60EF-3C45-A6FD-0EC980EA6D9A}" type="CELLRANGE">
+                    <a:fld id="{1E619280-9CAD-C14E-AF75-DA25950D1113}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10939,7 +10939,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{08C6C62E-842D-9F40-9D13-1D53344E9064}" type="CELLRANGE">
+                    <a:fld id="{C625D3F1-B25A-FC4F-83DF-4C8FF2537920}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10973,7 +10973,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3B8A2C23-801A-A14C-B336-DE53D9D1F777}" type="CELLRANGE">
+                    <a:fld id="{4A22944C-232C-8040-ACFA-F63AEBEE3975}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -11007,7 +11007,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FE549127-C35C-624A-AB10-8A0FD38227C8}" type="CELLRANGE">
+                    <a:fld id="{397CB677-C9F7-C54F-B9A6-5F69B5307481}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13238,8 +13238,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{309C7BF0-EB9D-6346-A799-FC47CF4A2EF2}" type="CELLRANGE">
-                      <a:rPr lang="zh-CN" altLang="en-US"/>
+                    <a:fld id="{44F9B5B0-FA78-544A-AD97-21096E095403}" type="CELLRANGE">
+                      <a:rPr lang="en-US" altLang="zh-CN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -13271,7 +13271,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7F5126BA-824D-634F-BCFF-41DFBCA6E049}" type="CELLRANGE">
+                    <a:fld id="{565E691D-0BB5-4F44-98EA-B191A7AB4BB8}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13305,7 +13305,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{90EDFEC5-F7D7-8940-A6F7-38320D828DF8}" type="CELLRANGE">
+                    <a:fld id="{28211A7D-72C9-CF44-9582-D7DF38AA6C06}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13339,7 +13339,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BACF01A6-C078-E845-B470-5C463ED432AD}" type="CELLRANGE">
+                    <a:fld id="{C9F66C36-44DE-D14D-8996-9B9D6ED25E92}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13373,7 +13373,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E5BA5666-B6D5-2F4D-9F2A-DA25D7679A79}" type="CELLRANGE">
+                    <a:fld id="{828AC4E2-5FAB-9B42-BC09-57D57A7D436A}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13407,7 +13407,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BD3ECF35-9561-3C40-A2A1-1723818B1F05}" type="CELLRANGE">
+                    <a:fld id="{5D66FC3F-96B0-A247-B10C-1E8C27BBDBDA}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13441,7 +13441,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3BEA2FEF-BD48-DB40-BB97-A1E4B880B3C2}" type="CELLRANGE">
+                    <a:fld id="{867C8062-6E5B-C04D-9306-F1DC4550AEAD}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13475,7 +13475,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{655316A2-33C2-2E41-8413-4A8789525476}" type="CELLRANGE">
+                    <a:fld id="{7AAB4B1C-F7A9-894E-A6D2-69FE0C0D886A}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="B2" s="21">
         <f ca="1">RANDBETWEEN(0,100)</f>
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -40979,7 +40979,7 @@
       </c>
       <c r="B3" s="21">
         <f t="shared" ref="B3:B11" ca="1" si="0">RANDBETWEEN(0,100)</f>
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -40994,7 +40994,7 @@
       </c>
       <c r="B4" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -41003,7 +41003,7 @@
       </c>
       <c r="B5" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -41012,7 +41012,7 @@
       </c>
       <c r="B6" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>91</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -41021,7 +41021,7 @@
       </c>
       <c r="B7" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -41030,7 +41030,7 @@
       </c>
       <c r="B8" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -41039,7 +41039,7 @@
       </c>
       <c r="B9" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>99</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -41048,7 +41048,7 @@
       </c>
       <c r="B10" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -41057,7 +41057,7 @@
       </c>
       <c r="B11" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:5">

--- a/excel/18图表与Offset函数.xlsx
+++ b/excel/18图表与Offset函数.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10909"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA8BD82-735B-A64D-98D6-74A2CF413394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C0273F-E33B-404E-9B08-13F4A43DE0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXCEL课件" sheetId="1" r:id="rId1"/>
@@ -5402,34 +5402,34 @@
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v> 2006/12/06</c:v>
+                  <c:v> 2007/04/17</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> 2006/12/07</c:v>
+                  <c:v> 2007/04/18</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v> 2006/12/08</c:v>
+                  <c:v> 2007/04/19</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v> 2006/12/11</c:v>
+                  <c:v> 2007/04/20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v> 2006/12/12</c:v>
+                  <c:v> 2007/04/23</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v> 2006/12/13</c:v>
+                  <c:v> 2007/04/24</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v> 2006/12/14</c:v>
+                  <c:v> 2007/04/25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v> 2006/12/15</c:v>
+                  <c:v> 2007/04/26</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v> 2006/12/18</c:v>
+                  <c:v> 2007/04/27</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v> 2006/12/19</c:v>
+                  <c:v> 2007/04/30</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5441,34 +5441,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>23504352</c:v>
+                  <c:v>17107981</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26170088</c:v>
+                  <c:v>24383468</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>22125894</c:v>
+                  <c:v>26114851</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20837233</c:v>
+                  <c:v>21106449</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>17400793</c:v>
+                  <c:v>30839757</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>25551184</c:v>
+                  <c:v>20434018</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>15818192</c:v>
+                  <c:v>27323654</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>22487599</c:v>
+                  <c:v>23952562</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>23940857</c:v>
+                  <c:v>36034578</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>18424502</c:v>
+                  <c:v>38233396</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5767,34 +5767,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>35</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>43</c:v>
+                  <c:v>91</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>52</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>43</c:v>
+                  <c:v>97</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>68</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>50</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>60</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>40</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>93</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7182,7 +7182,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BB96EB1A-A703-334A-B5F3-C5EF1164DBBE}" type="CELLRANGE">
+                    <a:fld id="{C78309F7-2302-8141-8794-9ABF39E61BF5}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7215,7 +7215,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8FC02C76-8C65-DD45-B349-7FF5BADB4F7A}" type="CELLRANGE">
+                    <a:fld id="{42A8DD0A-B7E7-BC47-BAFD-9CA629F9FBD3}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7249,7 +7249,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0EBB2D3B-394A-174E-81EC-378252E71DBC}" type="CELLRANGE">
+                    <a:fld id="{DEB90D66-1FD6-8F4F-8B1D-7613B852C443}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7283,7 +7283,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EE9FD751-50B8-EA44-91A4-FAA5044FE4F9}" type="CELLRANGE">
+                    <a:fld id="{8EF2C154-4370-344F-A161-7AA7E69B9468}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7317,7 +7317,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8985506C-217B-8E47-B9C2-001E9AC4E228}" type="CELLRANGE">
+                    <a:fld id="{B125B21D-8C66-2945-AF55-95103F03CF8D}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7351,7 +7351,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4991E127-E0A5-1B40-95C1-412CDA3364BB}" type="CELLRANGE">
+                    <a:fld id="{C57107C2-342B-3348-A4D9-E55AD9AC36D0}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7385,7 +7385,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9AF4FB9B-2993-8F4D-9B27-968617EA38B6}" type="CELLRANGE">
+                    <a:fld id="{CB966DC6-A8A7-8940-8889-1A1D30DB468D}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7419,7 +7419,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{527A3373-473A-6241-A6F9-57187D6284D2}" type="CELLRANGE">
+                    <a:fld id="{BFDD64C1-8BA9-7B44-A147-03E8ED0851C1}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7453,7 +7453,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3DABFF05-1D9E-7245-8582-3384B415A81C}" type="CELLRANGE">
+                    <a:fld id="{D54BAA2C-DCDF-DD4F-83BD-B4115C500CE5}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7487,7 +7487,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6D44C7E4-5146-2B42-B5D2-976307A957A8}" type="CELLRANGE">
+                    <a:fld id="{5381A31A-38B3-7D44-9E11-C02E590C93E0}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10667,7 +10667,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B0EC9C77-57F3-6042-9885-BC5B7C98A499}" type="CELLRANGE">
+                    <a:fld id="{70912845-1B81-D747-A860-3B8C57497A9D}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10701,7 +10701,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F02DFB9E-4299-5C4C-AC10-90D321ED0995}" type="CELLRANGE">
+                    <a:fld id="{A0082836-BD6C-AF4B-80DC-AE30B9884DDA}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10735,7 +10735,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CD5D7E2B-348F-7742-8FFC-517DFB61885B}" type="CELLRANGE">
+                    <a:fld id="{9C7A023D-1805-8241-8B37-FE02BC0762A6}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10769,7 +10769,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{113D75BD-9392-E747-8E7E-6BFF6226CEB4}" type="CELLRANGE">
+                    <a:fld id="{31D7D93D-BB80-8444-B59D-A78E66092DF0}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10803,7 +10803,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3D1982F4-07C9-854F-9AB0-7343987269C4}" type="CELLRANGE">
+                    <a:fld id="{D04C65C8-2D90-9245-BC79-69761B2894B3}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10837,7 +10837,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{543C366E-A16B-9E4B-9800-30E42A86E4C0}" type="CELLRANGE">
+                    <a:fld id="{6ECD57A4-C925-9046-AC3D-BDF5FA599102}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10871,7 +10871,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{38A9E32D-FA9A-EF49-A80F-C77FDC572B54}" type="CELLRANGE">
+                    <a:fld id="{B1BCAE6A-730E-9446-BB38-7A862244F60A}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10905,7 +10905,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1E619280-9CAD-C14E-AF75-DA25950D1113}" type="CELLRANGE">
+                    <a:fld id="{9FEE474F-479B-C442-8ECB-74C732C3E23B}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10939,7 +10939,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C625D3F1-B25A-FC4F-83DF-4C8FF2537920}" type="CELLRANGE">
+                    <a:fld id="{E97ADD48-CF7C-1144-B8EF-33D8BEE000AC}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10973,7 +10973,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4A22944C-232C-8040-ACFA-F63AEBEE3975}" type="CELLRANGE">
+                    <a:fld id="{79162BAE-5A8A-9A40-A7BD-6D0FF1B742A8}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -11007,7 +11007,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{397CB677-C9F7-C54F-B9A6-5F69B5307481}" type="CELLRANGE">
+                    <a:fld id="{C8949D90-78B2-6642-B0D1-3D357ECAB729}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13271,7 +13271,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{565E691D-0BB5-4F44-98EA-B191A7AB4BB8}" type="CELLRANGE">
+                    <a:fld id="{C9593814-8CB9-6F4F-B06A-35C2563A65D9}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13305,7 +13305,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{28211A7D-72C9-CF44-9582-D7DF38AA6C06}" type="CELLRANGE">
+                    <a:fld id="{2D28E229-844A-1249-9EC7-C934A9474144}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13339,7 +13339,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C9F66C36-44DE-D14D-8996-9B9D6ED25E92}" type="CELLRANGE">
+                    <a:fld id="{C2A9B610-73D3-C347-8F4F-A9D17822DA21}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13373,7 +13373,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{828AC4E2-5FAB-9B42-BC09-57D57A7D436A}" type="CELLRANGE">
+                    <a:fld id="{23EB547F-5C45-C845-85F9-5B8B313F0E2F}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13407,7 +13407,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5D66FC3F-96B0-A247-B10C-1E8C27BBDBDA}" type="CELLRANGE">
+                    <a:fld id="{21714C68-5A1F-974F-AD76-2482C0127B8C}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13441,7 +13441,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{867C8062-6E5B-C04D-9306-F1DC4550AEAD}" type="CELLRANGE">
+                    <a:fld id="{75144A0E-E7BE-5743-B04A-D2B9D165B857}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13475,7 +13475,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7AAB4B1C-F7A9-894E-A6D2-69FE0C0D886A}" type="CELLRANGE">
+                    <a:fld id="{18561327-5D21-4241-9C43-49F211E7BCCC}" type="CELLRANGE">
                       <a:rPr lang="zh-CN" altLang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -34547,7 +34547,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="15" fmlaLink="$C$45" horiz="1" max="100" min="1" noThreeD="1" page="10"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="15" fmlaLink="$C$45" horiz="1" max="100" min="1" noThreeD="1" page="10" val="87"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
@@ -39812,7 +39812,7 @@
         <v>191</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="D45" s="51" t="s">
         <v>19</v>
@@ -39830,11 +39830,11 @@
       </c>
       <c r="D46" s="52" t="str" cm="1">
         <f t="array" ref="D46">INDEX(A46:A144,$C$45)</f>
-        <v xml:space="preserve"> 2006/12/06</v>
+        <v xml:space="preserve"> 2007/04/17</v>
       </c>
       <c r="E46" s="52" cm="1">
         <f t="array" ref="E46">INDEX(B46:B144,$C$45)</f>
-        <v>23504352</v>
+        <v>17107981</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -39846,11 +39846,11 @@
       </c>
       <c r="D47" s="52" t="str" cm="1">
         <f t="array" ref="D47">INDEX(A47:A145,$C$45)</f>
-        <v xml:space="preserve"> 2006/12/07</v>
+        <v xml:space="preserve"> 2007/04/18</v>
       </c>
       <c r="E47" s="52" cm="1">
         <f t="array" ref="E47">INDEX(B47:B145,$C$45)</f>
-        <v>26170088</v>
+        <v>24383468</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -39862,11 +39862,11 @@
       </c>
       <c r="D48" s="52" t="str" cm="1">
         <f t="array" ref="D48">INDEX(A48:A146,$C$45)</f>
-        <v xml:space="preserve"> 2006/12/08</v>
+        <v xml:space="preserve"> 2007/04/19</v>
       </c>
       <c r="E48" s="52" cm="1">
         <f t="array" ref="E48">INDEX(B48:B146,$C$45)</f>
-        <v>22125894</v>
+        <v>26114851</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -39878,11 +39878,11 @@
       </c>
       <c r="D49" s="52" t="str" cm="1">
         <f t="array" ref="D49">INDEX(A49:A147,$C$45)</f>
-        <v xml:space="preserve"> 2006/12/11</v>
+        <v xml:space="preserve"> 2007/04/20</v>
       </c>
       <c r="E49" s="52" cm="1">
         <f t="array" ref="E49">INDEX(B49:B147,$C$45)</f>
-        <v>20837233</v>
+        <v>21106449</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -39894,11 +39894,11 @@
       </c>
       <c r="D50" s="52" t="str" cm="1">
         <f t="array" ref="D50">INDEX(A50:A148,$C$45)</f>
-        <v xml:space="preserve"> 2006/12/12</v>
+        <v xml:space="preserve"> 2007/04/23</v>
       </c>
       <c r="E50" s="52" cm="1">
         <f t="array" ref="E50">INDEX(B50:B148,$C$45)</f>
-        <v>17400793</v>
+        <v>30839757</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -39910,11 +39910,11 @@
       </c>
       <c r="D51" s="52" t="str" cm="1">
         <f t="array" ref="D51">INDEX(A51:A149,$C$45)</f>
-        <v xml:space="preserve"> 2006/12/13</v>
+        <v xml:space="preserve"> 2007/04/24</v>
       </c>
       <c r="E51" s="52" cm="1">
         <f t="array" ref="E51">INDEX(B51:B149,$C$45)</f>
-        <v>25551184</v>
+        <v>20434018</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -39926,11 +39926,11 @@
       </c>
       <c r="D52" s="52" t="str" cm="1">
         <f t="array" ref="D52">INDEX(A52:A150,$C$45)</f>
-        <v xml:space="preserve"> 2006/12/14</v>
+        <v xml:space="preserve"> 2007/04/25</v>
       </c>
       <c r="E52" s="52" cm="1">
         <f t="array" ref="E52">INDEX(B52:B150,$C$45)</f>
-        <v>15818192</v>
+        <v>27323654</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -39942,11 +39942,11 @@
       </c>
       <c r="D53" s="52" t="str" cm="1">
         <f t="array" ref="D53">INDEX(A53:A151,$C$45)</f>
-        <v xml:space="preserve"> 2006/12/15</v>
+        <v xml:space="preserve"> 2007/04/26</v>
       </c>
       <c r="E53" s="52" cm="1">
         <f t="array" ref="E53">INDEX(B53:B151,$C$45)</f>
-        <v>22487599</v>
+        <v>23952562</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -39958,11 +39958,11 @@
       </c>
       <c r="D54" s="52" t="str" cm="1">
         <f t="array" ref="D54">INDEX(A54:A152,$C$45)</f>
-        <v xml:space="preserve"> 2006/12/18</v>
+        <v xml:space="preserve"> 2007/04/27</v>
       </c>
       <c r="E54" s="52" cm="1">
         <f t="array" ref="E54">INDEX(B54:B152,$C$45)</f>
-        <v>23940857</v>
+        <v>36034578</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -39974,11 +39974,11 @@
       </c>
       <c r="D55" s="52" t="str" cm="1">
         <f t="array" ref="D55">INDEX(A55:A153,$C$45)</f>
-        <v xml:space="preserve"> 2006/12/19</v>
+        <v xml:space="preserve"> 2007/04/30</v>
       </c>
       <c r="E55" s="52" cm="1">
         <f t="array" ref="E55">INDEX(B55:B153,$C$45)</f>
-        <v>18424502</v>
+        <v>38233396</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -40964,7 +40964,7 @@
       </c>
       <c r="B2" s="21">
         <f ca="1">RANDBETWEEN(0,100)</f>
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -40979,7 +40979,7 @@
       </c>
       <c r="B3" s="21">
         <f t="shared" ref="B3:B11" ca="1" si="0">RANDBETWEEN(0,100)</f>
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -40994,7 +40994,7 @@
       </c>
       <c r="B4" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -41003,7 +41003,7 @@
       </c>
       <c r="B5" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -41012,7 +41012,7 @@
       </c>
       <c r="B6" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -41021,7 +41021,7 @@
       </c>
       <c r="B7" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -41030,7 +41030,7 @@
       </c>
       <c r="B8" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -41039,7 +41039,7 @@
       </c>
       <c r="B9" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -41048,7 +41048,7 @@
       </c>
       <c r="B10" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -41057,7 +41057,7 @@
       </c>
       <c r="B11" s="21">
         <f t="shared" ca="1" si="0"/>
-        <v>93</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:5">
